--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1220,48 +1220,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132038582</v>
+        <v>134675398</v>
       </c>
       <c r="B7" t="n">
-        <v>91937</v>
+        <v>80489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469505</v>
+        <v>469575</v>
       </c>
       <c r="R7" t="n">
-        <v>6859396</v>
+        <v>6859402</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,22 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,60 +1305,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129576469</v>
+        <v>132038582</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>91937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469556</v>
+        <v>469505</v>
       </c>
       <c r="R8" t="n">
-        <v>6859284</v>
+        <v>6859396</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,17 +1382,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,19 +1412,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129577131</v>
+        <v>129576469</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469606</v>
+        <v>469556</v>
       </c>
       <c r="R9" t="n">
-        <v>6859286</v>
+        <v>6859284</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129577275</v>
+        <v>129577131</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469530</v>
+        <v>469606</v>
       </c>
       <c r="R10" t="n">
-        <v>6859327</v>
+        <v>6859286</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129577297</v>
+        <v>129577275</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469531</v>
+        <v>469530</v>
       </c>
       <c r="R11" t="n">
         <v>6859327</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129577349</v>
+        <v>129577297</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469490</v>
+        <v>469531</v>
       </c>
       <c r="R12" t="n">
-        <v>6859342</v>
+        <v>6859327</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129577427</v>
+        <v>129577349</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469477</v>
+        <v>469490</v>
       </c>
       <c r="R13" t="n">
-        <v>6859330</v>
+        <v>6859342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129577487</v>
+        <v>129577427</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469478</v>
+        <v>469477</v>
       </c>
       <c r="R14" t="n">
-        <v>6859332</v>
+        <v>6859330</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129633776</v>
+        <v>129577487</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2042,14 +2042,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Frängvallen, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469481</v>
+        <v>469478</v>
       </c>
       <c r="R15" t="n">
-        <v>6859431</v>
+        <v>6859332</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,22 +2076,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,19 +2096,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129633777</v>
+        <v>129633776</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469479</v>
+        <v>469481</v>
       </c>
       <c r="R16" t="n">
-        <v>6859435</v>
+        <v>6859431</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129633778</v>
+        <v>129633777</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2260,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469478</v>
+        <v>469479</v>
       </c>
       <c r="R17" t="n">
-        <v>6859443</v>
+        <v>6859435</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,7 +2285,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2305,7 +2295,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129633779</v>
+        <v>129633778</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469468</v>
+        <v>469478</v>
       </c>
       <c r="R18" t="n">
-        <v>6859448</v>
+        <v>6859443</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,7 +2392,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2412,7 +2402,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129648005</v>
+        <v>129633779</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2470,14 +2460,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Frängvallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469734</v>
+        <v>469468</v>
       </c>
       <c r="R19" t="n">
-        <v>6859468</v>
+        <v>6859448</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2507,9 +2497,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,19 +2524,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129648006</v>
+        <v>129648005</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469487</v>
+        <v>469734</v>
       </c>
       <c r="R20" t="n">
-        <v>6859386</v>
+        <v>6859468</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129648007</v>
+        <v>129648006</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469494</v>
+        <v>469487</v>
       </c>
       <c r="R21" t="n">
-        <v>6859381</v>
+        <v>6859386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129648008</v>
+        <v>129648007</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469484</v>
+        <v>469494</v>
       </c>
       <c r="R22" t="n">
-        <v>6859409</v>
+        <v>6859381</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129648009</v>
+        <v>129648008</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2865,7 +2865,7 @@
         <v>469484</v>
       </c>
       <c r="R23" t="n">
-        <v>6859413</v>
+        <v>6859409</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129648010</v>
+        <v>129648009</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469477</v>
+        <v>469484</v>
       </c>
       <c r="R24" t="n">
-        <v>6859426</v>
+        <v>6859413</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129648011</v>
+        <v>129648010</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469471</v>
+        <v>469477</v>
       </c>
       <c r="R25" t="n">
-        <v>6859430</v>
+        <v>6859426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129648012</v>
+        <v>129648011</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469464</v>
+        <v>469471</v>
       </c>
       <c r="R26" t="n">
-        <v>6859442</v>
+        <v>6859430</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,7 +3215,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129648015</v>
+        <v>129648012</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469480</v>
+        <v>469464</v>
       </c>
       <c r="R27" t="n">
-        <v>6859429</v>
+        <v>6859442</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129648413</v>
+        <v>129648015</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469761</v>
+        <v>469480</v>
       </c>
       <c r="R28" t="n">
-        <v>6859336</v>
+        <v>6859429</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,19 +3397,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129657344</v>
+        <v>129648413</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469485</v>
+        <v>469761</v>
       </c>
       <c r="R29" t="n">
-        <v>6859429</v>
+        <v>6859336</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3488,26 +3488,25 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129657346</v>
+        <v>129657344</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3542,10 +3541,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469476</v>
+        <v>469485</v>
       </c>
       <c r="R30" t="n">
-        <v>6859422</v>
+        <v>6859429</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3605,7 +3604,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129657347</v>
+        <v>129657346</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3640,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469480</v>
+        <v>469476</v>
       </c>
       <c r="R31" t="n">
-        <v>6859380</v>
+        <v>6859422</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3703,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132038618</v>
+        <v>129657347</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3734,17 +3733,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469476</v>
+        <v>469480</v>
       </c>
       <c r="R32" t="n">
-        <v>6859454</v>
+        <v>6859380</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3771,24 +3770,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3804,19 +3788,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132038622</v>
+        <v>132038618</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -3851,10 +3835,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>469479</v>
+        <v>469476</v>
       </c>
       <c r="R33" t="n">
-        <v>6859427</v>
+        <v>6859454</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3886,7 +3870,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3896,12 +3880,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På granstam</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3929,7 +3913,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132038631</v>
+        <v>132038622</v>
       </c>
       <c r="B34" t="n">
         <v>79373</v>
@@ -3964,10 +3948,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>469598</v>
+        <v>469479</v>
       </c>
       <c r="R34" t="n">
-        <v>6859376</v>
+        <v>6859427</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3999,7 +3983,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4009,7 +3993,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På granstam</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4018,6 +4007,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4036,48 +4026,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129633773</v>
+        <v>132038631</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Frängvallen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469482</v>
+        <v>469598</v>
       </c>
       <c r="R35" t="n">
-        <v>6859400</v>
+        <v>6859376</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4106,7 +4096,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4116,7 +4106,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4131,60 +4121,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132038593</v>
+        <v>134675467</v>
       </c>
       <c r="B36" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469487</v>
+        <v>469586</v>
       </c>
       <c r="R36" t="n">
-        <v>6859393</v>
+        <v>6859366</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4208,22 +4198,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4238,60 +4218,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132038590</v>
+        <v>134676077</v>
       </c>
       <c r="B37" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469512</v>
+        <v>469654</v>
       </c>
       <c r="R37" t="n">
-        <v>6859403</v>
+        <v>6859328</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4315,22 +4295,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4345,22 +4315,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132038591</v>
+        <v>129633773</v>
       </c>
       <c r="B38" t="n">
-        <v>80488</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,37 +4338,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frängvallen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469464</v>
+        <v>469482</v>
       </c>
       <c r="R38" t="n">
-        <v>6859417</v>
+        <v>6859400</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4427,7 +4397,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4437,7 +4407,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4452,22 +4422,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129647998</v>
+        <v>132038593</v>
       </c>
       <c r="B39" t="n">
-        <v>58114</v>
+        <v>79130</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4475,37 +4445,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
         <v>469487</v>
       </c>
       <c r="R39" t="n">
-        <v>6859386</v>
+        <v>6859393</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4532,9 +4502,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,22 +4529,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129648407</v>
+        <v>132038590</v>
       </c>
       <c r="B40" t="n">
-        <v>58114</v>
+        <v>80488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4572,45 +4552,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>469484</v>
+        <v>469512</v>
       </c>
       <c r="R40" t="n">
-        <v>6859352</v>
+        <v>6859403</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4637,9 +4609,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4654,22 +4636,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129657334</v>
+        <v>132038591</v>
       </c>
       <c r="B41" t="n">
-        <v>58114</v>
+        <v>80488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4677,37 +4659,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469478</v>
+        <v>469464</v>
       </c>
       <c r="R41" t="n">
-        <v>6859422</v>
+        <v>6859417</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4734,9 +4716,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4751,22 +4743,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132038583</v>
+        <v>129647998</v>
       </c>
       <c r="B42" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4791,24 +4783,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469463</v>
+        <v>469487</v>
       </c>
       <c r="R42" t="n">
-        <v>6859422</v>
+        <v>6859386</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4835,24 +4823,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4867,22 +4840,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129633772</v>
+        <v>129648407</v>
       </c>
       <c r="B43" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4890,34 +4863,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Frängvallen, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469482</v>
+        <v>469484</v>
       </c>
       <c r="R43" t="n">
-        <v>6859388</v>
+        <v>6859352</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4947,19 +4928,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4974,22 +4945,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132038592</v>
+        <v>129657334</v>
       </c>
       <c r="B44" t="n">
-        <v>58079</v>
+        <v>58114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4997,37 +4968,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469603</v>
+        <v>469478</v>
       </c>
       <c r="R44" t="n">
-        <v>6859383</v>
+        <v>6859422</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5054,19 +5025,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5081,74 +5042,64 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129602811</v>
+        <v>132038583</v>
       </c>
       <c r="B45" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469660</v>
+        <v>469463</v>
       </c>
       <c r="R45" t="n">
-        <v>6859439</v>
+        <v>6859422</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5177,7 +5128,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5187,7 +5138,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5214,45 +5170,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129648410</v>
+        <v>129633772</v>
       </c>
       <c r="B46" t="n">
-        <v>99118</v>
+        <v>58057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Frängvallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469726</v>
+        <v>469482</v>
       </c>
       <c r="R46" t="n">
-        <v>6859290</v>
+        <v>6859388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5282,9 +5238,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5299,44 +5265,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132038598</v>
+        <v>132038592</v>
       </c>
       <c r="B47" t="n">
-        <v>99195</v>
+        <v>58079</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5346,10 +5312,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469533</v>
+        <v>469603</v>
       </c>
       <c r="R47" t="n">
-        <v>6859346</v>
+        <v>6859383</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5381,7 +5347,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5391,7 +5357,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5418,48 +5384,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132038599</v>
+        <v>134675963</v>
       </c>
       <c r="B48" t="n">
-        <v>99195</v>
+        <v>108205</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469528</v>
+        <v>469655</v>
       </c>
       <c r="R48" t="n">
-        <v>6859347</v>
+        <v>6859352</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5483,22 +5449,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5513,60 +5469,69 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132038600</v>
+        <v>134678455</v>
       </c>
       <c r="B49" t="n">
-        <v>99195</v>
+        <v>99099</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>469464</v>
+        <v>469482</v>
       </c>
       <c r="R49" t="n">
-        <v>6859415</v>
+        <v>6859439</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5590,22 +5555,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5620,60 +5575,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132038601</v>
+        <v>134675994</v>
       </c>
       <c r="B50" t="n">
-        <v>99195</v>
+        <v>108274</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469448</v>
+        <v>469655</v>
       </c>
       <c r="R50" t="n">
-        <v>6859488</v>
+        <v>6859352</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5697,22 +5652,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5727,60 +5672,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132038608</v>
+        <v>134675983</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>110150</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469511</v>
+        <v>469655</v>
       </c>
       <c r="R51" t="n">
-        <v>6859411</v>
+        <v>6859352</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5804,22 +5749,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5834,22 +5769,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132038609</v>
+        <v>129602811</v>
       </c>
       <c r="B52" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5874,20 +5809,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469467</v>
+        <v>469660</v>
       </c>
       <c r="R52" t="n">
-        <v>6859441</v>
+        <v>6859439</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5916,7 +5865,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5926,7 +5875,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5953,30 +5902,34 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129648001</v>
+        <v>129648410</v>
       </c>
       <c r="B53" t="n">
-        <v>97977</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5984,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>469753</v>
+        <v>469726</v>
       </c>
       <c r="R53" t="n">
-        <v>6859437</v>
+        <v>6859290</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6028,22 +5981,1630 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132038598</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>469533</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6859346</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132038599</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>469528</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6859347</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132038600</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>469464</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6859415</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132038601</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>469448</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6859488</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132038608</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>469511</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6859411</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132038609</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>469467</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6859441</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134674521</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>469509</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6859411</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134675822</v>
+      </c>
+      <c r="B61" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>469649</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6859353</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129648001</v>
+      </c>
+      <c r="B62" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Frägnvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>469753</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6859437</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
           <t>Göran Ehn</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX62" t="inlineStr">
         <is>
           <t>Göran Ehn</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134674574</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>469517</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6859380</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134674601</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>469529</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6859380</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134675109</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>469556</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6859367</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134675710</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>469628</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6859357</v>
+      </c>
+      <c r="S66" t="n">
+        <v>20</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134675713</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>469623</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6859347</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134675870</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>469615</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6859312</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134676123</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>469670</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6859325</v>
+      </c>
+      <c r="S69" t="n">
+        <v>20</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4949,48 +4949,62 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129647998</v>
+        <v>135254319</v>
       </c>
       <c r="B44" t="n">
-        <v>58114</v>
+        <v>57162</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469487</v>
+        <v>469455</v>
       </c>
       <c r="R44" t="n">
-        <v>6859386</v>
+        <v>6859471</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5014,12 +5028,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5034,19 +5048,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129648407</v>
+        <v>129647998</v>
       </c>
       <c r="B45" t="n">
         <v>58114</v>
@@ -5075,24 +5089,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469484</v>
+        <v>469487</v>
       </c>
       <c r="R45" t="n">
-        <v>6859352</v>
+        <v>6859386</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5139,19 +5145,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129657334</v>
+        <v>129648407</v>
       </c>
       <c r="B46" t="n">
         <v>58114</v>
@@ -5180,19 +5186,27 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469478</v>
+        <v>469484</v>
       </c>
       <c r="R46" t="n">
-        <v>6859422</v>
+        <v>6859352</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5236,22 +5250,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132038583</v>
+        <v>129657334</v>
       </c>
       <c r="B47" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5276,24 +5290,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469463</v>
+        <v>469478</v>
       </c>
       <c r="R47" t="n">
         <v>6859422</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5320,24 +5330,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5352,22 +5347,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129633772</v>
+        <v>132038583</v>
       </c>
       <c r="B48" t="n">
-        <v>58057</v>
+        <v>58136</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,37 +5370,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Frängvallen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469482</v>
+        <v>469463</v>
       </c>
       <c r="R48" t="n">
-        <v>6859388</v>
+        <v>6859422</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5434,7 +5433,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5444,7 +5443,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5459,22 +5463,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132038592</v>
+        <v>135254338</v>
       </c>
       <c r="B49" t="n">
-        <v>58079</v>
+        <v>58136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5482,37 +5486,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>469603</v>
+        <v>469453</v>
       </c>
       <c r="R49" t="n">
-        <v>6859383</v>
+        <v>6859464</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5536,22 +5549,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5566,60 +5569,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134675963</v>
+        <v>129633772</v>
       </c>
       <c r="B50" t="n">
-        <v>108205</v>
+        <v>58057</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220083</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Frängvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469655</v>
+        <v>469482</v>
       </c>
       <c r="R50" t="n">
-        <v>6859352</v>
+        <v>6859388</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5643,12 +5646,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5663,69 +5676,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134678455</v>
+        <v>132038592</v>
       </c>
       <c r="B51" t="n">
-        <v>99099</v>
+        <v>58079</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220093</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469482</v>
+        <v>469603</v>
       </c>
       <c r="R51" t="n">
-        <v>6859439</v>
+        <v>6859383</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5749,12 +5753,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5769,22 +5783,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134675994</v>
+        <v>134675963</v>
       </c>
       <c r="B52" t="n">
-        <v>108274</v>
+        <v>108205</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5792,21 +5806,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5878,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134675983</v>
+        <v>134678455</v>
       </c>
       <c r="B53" t="n">
-        <v>110150</v>
+        <v>99099</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5889,37 +5903,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220294</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>469655</v>
+        <v>469482</v>
       </c>
       <c r="R53" t="n">
-        <v>6859352</v>
+        <v>6859439</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5963,74 +5986,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129602811</v>
+        <v>134675994</v>
       </c>
       <c r="B54" t="n">
-        <v>99118</v>
+        <v>108274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>469660</v>
+        <v>469655</v>
       </c>
       <c r="R54" t="n">
-        <v>6859439</v>
+        <v>6859352</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6054,22 +6063,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6084,60 +6083,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129648410</v>
+        <v>134675983</v>
       </c>
       <c r="B55" t="n">
-        <v>99118</v>
+        <v>110150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469726</v>
+        <v>469655</v>
       </c>
       <c r="R55" t="n">
-        <v>6859290</v>
+        <v>6859352</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6161,12 +6160,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6181,22 +6180,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132038598</v>
+        <v>129602811</v>
       </c>
       <c r="B56" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6221,20 +6220,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>469533</v>
+        <v>469660</v>
       </c>
       <c r="R56" t="n">
-        <v>6859346</v>
+        <v>6859439</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6263,7 +6276,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6273,7 +6286,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6300,10 +6313,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132038599</v>
+        <v>129648410</v>
       </c>
       <c r="B57" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6331,17 +6344,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>469528</v>
+        <v>469726</v>
       </c>
       <c r="R57" t="n">
-        <v>6859347</v>
+        <v>6859290</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6368,19 +6381,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6395,19 +6398,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132038600</v>
+        <v>132038598</v>
       </c>
       <c r="B58" t="n">
         <v>99195</v>
@@ -6442,10 +6445,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469464</v>
+        <v>469533</v>
       </c>
       <c r="R58" t="n">
-        <v>6859415</v>
+        <v>6859346</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6477,7 +6480,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6487,7 +6490,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6514,7 +6517,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132038601</v>
+        <v>132038599</v>
       </c>
       <c r="B59" t="n">
         <v>99195</v>
@@ -6549,10 +6552,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>469448</v>
+        <v>469528</v>
       </c>
       <c r="R59" t="n">
-        <v>6859488</v>
+        <v>6859347</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6584,7 +6587,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6594,7 +6597,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6621,7 +6624,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132038608</v>
+        <v>132038600</v>
       </c>
       <c r="B60" t="n">
         <v>99195</v>
@@ -6656,10 +6659,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469511</v>
+        <v>469464</v>
       </c>
       <c r="R60" t="n">
-        <v>6859411</v>
+        <v>6859415</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6691,7 +6694,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6701,7 +6704,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6728,7 +6731,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132038609</v>
+        <v>132038601</v>
       </c>
       <c r="B61" t="n">
         <v>99195</v>
@@ -6763,10 +6766,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469467</v>
+        <v>469448</v>
       </c>
       <c r="R61" t="n">
-        <v>6859441</v>
+        <v>6859488</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6798,7 +6801,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6808,7 +6811,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6835,7 +6838,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134674521</v>
+        <v>132038608</v>
       </c>
       <c r="B62" t="n">
         <v>99195</v>
@@ -6866,17 +6869,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469509</v>
+        <v>469511</v>
       </c>
       <c r="R62" t="n">
         <v>6859411</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6900,12 +6903,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6920,19 +6933,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134917738</v>
+        <v>132038609</v>
       </c>
       <c r="B63" t="n">
         <v>99195</v>
@@ -6960,29 +6973,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469433</v>
+        <v>469467</v>
       </c>
       <c r="R63" t="n">
-        <v>6859503</v>
+        <v>6859441</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7006,12 +7010,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7026,44 +7040,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134675822</v>
+        <v>134674521</v>
       </c>
       <c r="B64" t="n">
-        <v>109924</v>
+        <v>99195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221184</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7073,13 +7087,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469649</v>
+        <v>469509</v>
       </c>
       <c r="R64" t="n">
-        <v>6859353</v>
+        <v>6859411</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7123,53 +7137,66 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129648001</v>
+        <v>134917738</v>
       </c>
       <c r="B65" t="n">
-        <v>97977</v>
+        <v>99195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469753</v>
+        <v>469433</v>
       </c>
       <c r="R65" t="n">
-        <v>6859437</v>
+        <v>6859503</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7196,12 +7223,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7210,29 +7237,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134674574</v>
+        <v>134675822</v>
       </c>
       <c r="B66" t="n">
-        <v>99217</v>
+        <v>109924</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7240,21 +7266,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>221184</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7264,13 +7290,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469517</v>
+        <v>469649</v>
       </c>
       <c r="R66" t="n">
-        <v>6859380</v>
+        <v>6859353</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7314,22 +7340,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134674601</v>
+        <v>129648001</v>
       </c>
       <c r="B67" t="n">
-        <v>99217</v>
+        <v>97977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7337,37 +7363,33 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>221944</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469529</v>
+        <v>469753</v>
       </c>
       <c r="R67" t="n">
-        <v>6859380</v>
+        <v>6859437</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7391,12 +7413,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7405,25 +7427,26 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134675109</v>
+        <v>134674574</v>
       </c>
       <c r="B68" t="n">
         <v>99217</v>
@@ -7458,13 +7481,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469556</v>
+        <v>469517</v>
       </c>
       <c r="R68" t="n">
-        <v>6859367</v>
+        <v>6859380</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7520,7 +7543,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134675710</v>
+        <v>134674601</v>
       </c>
       <c r="B69" t="n">
         <v>99217</v>
@@ -7555,13 +7578,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>469628</v>
+        <v>469529</v>
       </c>
       <c r="R69" t="n">
-        <v>6859357</v>
+        <v>6859380</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7605,19 +7628,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134675713</v>
+        <v>134675109</v>
       </c>
       <c r="B70" t="n">
         <v>99217</v>
@@ -7652,10 +7675,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>469623</v>
+        <v>469556</v>
       </c>
       <c r="R70" t="n">
-        <v>6859347</v>
+        <v>6859367</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7714,7 +7737,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134675870</v>
+        <v>134675710</v>
       </c>
       <c r="B71" t="n">
         <v>99217</v>
@@ -7749,13 +7772,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469615</v>
+        <v>469628</v>
       </c>
       <c r="R71" t="n">
-        <v>6859312</v>
+        <v>6859357</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7799,19 +7822,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134676123</v>
+        <v>134675713</v>
       </c>
       <c r="B72" t="n">
         <v>99217</v>
@@ -7846,13 +7869,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469670</v>
+        <v>469623</v>
       </c>
       <c r="R72" t="n">
-        <v>6859325</v>
+        <v>6859347</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7896,60 +7919,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134918089</v>
+        <v>134675870</v>
       </c>
       <c r="B73" t="n">
-        <v>79963</v>
+        <v>99217</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469469</v>
+        <v>469615</v>
       </c>
       <c r="R73" t="n">
-        <v>6859389</v>
+        <v>6859312</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7973,12 +7996,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8002,6 +8025,200 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134676123</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>469670</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6859325</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>134918089</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>469469</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6859389</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,45 +1414,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132038582</v>
+        <v>135465062</v>
       </c>
       <c r="B9" t="n">
-        <v>91937</v>
+        <v>80489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469505</v>
+        <v>469515</v>
       </c>
       <c r="R9" t="n">
-        <v>6859396</v>
+        <v>6859399</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1479,22 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,60 +1499,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129576469</v>
+        <v>132038582</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>91937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469556</v>
+        <v>469505</v>
       </c>
       <c r="R10" t="n">
-        <v>6859284</v>
+        <v>6859396</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,17 +1576,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,19 +1606,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129577131</v>
+        <v>129576469</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469606</v>
+        <v>469556</v>
       </c>
       <c r="R11" t="n">
-        <v>6859286</v>
+        <v>6859284</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129577275</v>
+        <v>129577131</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469530</v>
+        <v>469606</v>
       </c>
       <c r="R12" t="n">
-        <v>6859327</v>
+        <v>6859286</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129577297</v>
+        <v>129577275</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469531</v>
+        <v>469530</v>
       </c>
       <c r="R13" t="n">
         <v>6859327</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129577349</v>
+        <v>129577297</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469490</v>
+        <v>469531</v>
       </c>
       <c r="R14" t="n">
-        <v>6859342</v>
+        <v>6859327</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129577427</v>
+        <v>129577349</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469477</v>
+        <v>469490</v>
       </c>
       <c r="R15" t="n">
-        <v>6859330</v>
+        <v>6859342</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129577487</v>
+        <v>129577427</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469478</v>
+        <v>469477</v>
       </c>
       <c r="R16" t="n">
-        <v>6859332</v>
+        <v>6859330</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129633776</v>
+        <v>129577487</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2236,14 +2236,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Frängvallen, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469481</v>
+        <v>469478</v>
       </c>
       <c r="R17" t="n">
-        <v>6859431</v>
+        <v>6859332</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,22 +2270,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2300,19 +2290,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129633777</v>
+        <v>129633776</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2347,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469479</v>
+        <v>469481</v>
       </c>
       <c r="R18" t="n">
-        <v>6859435</v>
+        <v>6859431</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129633778</v>
+        <v>129633777</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2454,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469478</v>
+        <v>469479</v>
       </c>
       <c r="R19" t="n">
-        <v>6859443</v>
+        <v>6859435</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,7 +2479,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2499,7 +2489,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129633779</v>
+        <v>129633778</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469468</v>
+        <v>469478</v>
       </c>
       <c r="R20" t="n">
-        <v>6859448</v>
+        <v>6859443</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2596,7 +2586,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2606,7 +2596,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129648005</v>
+        <v>129633779</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2664,14 +2654,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Frängvallen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469734</v>
+        <v>469468</v>
       </c>
       <c r="R21" t="n">
-        <v>6859468</v>
+        <v>6859448</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,9 +2691,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,19 +2718,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129648006</v>
+        <v>129648005</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469487</v>
+        <v>469734</v>
       </c>
       <c r="R22" t="n">
-        <v>6859386</v>
+        <v>6859468</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129648007</v>
+        <v>129648006</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469494</v>
+        <v>469487</v>
       </c>
       <c r="R23" t="n">
-        <v>6859381</v>
+        <v>6859386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129648008</v>
+        <v>129648007</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469484</v>
+        <v>469494</v>
       </c>
       <c r="R24" t="n">
-        <v>6859409</v>
+        <v>6859381</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129648009</v>
+        <v>129648008</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3059,7 +3059,7 @@
         <v>469484</v>
       </c>
       <c r="R25" t="n">
-        <v>6859413</v>
+        <v>6859409</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129648010</v>
+        <v>129648009</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469477</v>
+        <v>469484</v>
       </c>
       <c r="R26" t="n">
-        <v>6859426</v>
+        <v>6859413</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,7 +3215,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129648011</v>
+        <v>129648010</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469471</v>
+        <v>469477</v>
       </c>
       <c r="R27" t="n">
-        <v>6859430</v>
+        <v>6859426</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129648012</v>
+        <v>129648011</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469464</v>
+        <v>469471</v>
       </c>
       <c r="R28" t="n">
-        <v>6859442</v>
+        <v>6859430</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129648015</v>
+        <v>129648012</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469480</v>
+        <v>469464</v>
       </c>
       <c r="R29" t="n">
-        <v>6859429</v>
+        <v>6859442</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129648413</v>
+        <v>129648015</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469761</v>
+        <v>469480</v>
       </c>
       <c r="R30" t="n">
-        <v>6859336</v>
+        <v>6859429</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3591,19 +3591,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129657344</v>
+        <v>129648413</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3638,13 +3638,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469485</v>
+        <v>469761</v>
       </c>
       <c r="R31" t="n">
-        <v>6859429</v>
+        <v>6859336</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3682,26 +3682,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129657346</v>
+        <v>129657344</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -3736,10 +3735,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469476</v>
+        <v>469485</v>
       </c>
       <c r="R32" t="n">
-        <v>6859422</v>
+        <v>6859429</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3799,7 +3798,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129657347</v>
+        <v>129657346</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -3834,10 +3833,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>469480</v>
+        <v>469476</v>
       </c>
       <c r="R33" t="n">
-        <v>6859380</v>
+        <v>6859422</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3897,10 +3896,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132038618</v>
+        <v>129657347</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3928,17 +3927,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>469476</v>
+        <v>469480</v>
       </c>
       <c r="R34" t="n">
-        <v>6859454</v>
+        <v>6859380</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3965,24 +3964,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,19 +3982,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132038622</v>
+        <v>132038618</v>
       </c>
       <c r="B35" t="n">
         <v>79373</v>
@@ -4045,10 +4029,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469479</v>
+        <v>469476</v>
       </c>
       <c r="R35" t="n">
-        <v>6859427</v>
+        <v>6859454</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4080,7 +4064,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4090,12 +4074,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På granstam</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,7 +4107,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132038631</v>
+        <v>132038622</v>
       </c>
       <c r="B36" t="n">
         <v>79373</v>
@@ -4158,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469598</v>
+        <v>469479</v>
       </c>
       <c r="R36" t="n">
-        <v>6859376</v>
+        <v>6859427</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4193,7 +4177,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4203,7 +4187,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På granstam</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4212,6 +4201,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4230,7 +4220,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134675467</v>
+        <v>132038631</v>
       </c>
       <c r="B37" t="n">
         <v>79373</v>
@@ -4261,17 +4251,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469586</v>
+        <v>469598</v>
       </c>
       <c r="R37" t="n">
-        <v>6859366</v>
+        <v>6859376</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4295,12 +4285,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4315,19 +4315,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134676077</v>
+        <v>134675467</v>
       </c>
       <c r="B38" t="n">
         <v>79373</v>
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469654</v>
+        <v>469586</v>
       </c>
       <c r="R38" t="n">
-        <v>6859328</v>
+        <v>6859366</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4412,60 +4412,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129633773</v>
+        <v>134676077</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Frängvallen, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>469482</v>
+        <v>469654</v>
       </c>
       <c r="R39" t="n">
-        <v>6859400</v>
+        <v>6859328</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4489,22 +4489,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4519,22 +4509,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132038593</v>
+        <v>129633773</v>
       </c>
       <c r="B40" t="n">
-        <v>79130</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4562,17 +4552,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frängvallen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>469487</v>
+        <v>469482</v>
       </c>
       <c r="R40" t="n">
-        <v>6859393</v>
+        <v>6859400</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4601,7 +4591,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4611,7 +4601,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4626,22 +4616,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132038590</v>
+        <v>132038593</v>
       </c>
       <c r="B41" t="n">
-        <v>80488</v>
+        <v>79130</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4649,21 +4639,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4673,10 +4663,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469512</v>
+        <v>469487</v>
       </c>
       <c r="R41" t="n">
-        <v>6859403</v>
+        <v>6859393</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4708,7 +4698,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4718,7 +4708,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4745,7 +4735,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132038591</v>
+        <v>132038590</v>
       </c>
       <c r="B42" t="n">
         <v>80488</v>
@@ -4780,10 +4770,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469464</v>
+        <v>469512</v>
       </c>
       <c r="R42" t="n">
-        <v>6859417</v>
+        <v>6859403</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4815,7 +4805,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4825,7 +4815,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4852,7 +4842,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134918047</v>
+        <v>132038591</v>
       </c>
       <c r="B43" t="n">
         <v>80488</v>
@@ -4883,17 +4873,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469466</v>
+        <v>469464</v>
       </c>
       <c r="R43" t="n">
-        <v>6859406</v>
+        <v>6859417</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4917,12 +4907,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4937,74 +4937,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135254319</v>
+        <v>134918047</v>
       </c>
       <c r="B44" t="n">
-        <v>57162</v>
+        <v>80488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469455</v>
+        <v>469466</v>
       </c>
       <c r="R44" t="n">
-        <v>6859471</v>
+        <v>6859406</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5028,12 +5014,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5048,22 +5034,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129647998</v>
+        <v>135465024</v>
       </c>
       <c r="B45" t="n">
-        <v>58114</v>
+        <v>80488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5071,34 +5057,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469487</v>
+        <v>469513</v>
       </c>
       <c r="R45" t="n">
-        <v>6859386</v>
+        <v>6859399</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5125,12 +5111,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5145,68 +5131,74 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129648407</v>
+        <v>135254319</v>
       </c>
       <c r="B46" t="n">
-        <v>58114</v>
+        <v>57162</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469484</v>
+        <v>469455</v>
       </c>
       <c r="R46" t="n">
-        <v>6859352</v>
+        <v>6859471</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5230,12 +5222,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5250,19 +5242,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129657334</v>
+        <v>129647998</v>
       </c>
       <c r="B47" t="n">
         <v>58114</v>
@@ -5297,13 +5289,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469478</v>
+        <v>469487</v>
       </c>
       <c r="R47" t="n">
-        <v>6859422</v>
+        <v>6859386</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5347,22 +5339,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132038583</v>
+        <v>129648407</v>
       </c>
       <c r="B48" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5387,24 +5379,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469463</v>
+        <v>469484</v>
       </c>
       <c r="R48" t="n">
-        <v>6859422</v>
+        <v>6859352</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5431,24 +5427,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5463,22 +5444,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135254338</v>
+        <v>129657334</v>
       </c>
       <c r="B49" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5503,29 +5484,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>469453</v>
+        <v>469478</v>
       </c>
       <c r="R49" t="n">
-        <v>6859464</v>
+        <v>6859422</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5549,12 +5521,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,22 +5541,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129633772</v>
+        <v>132038583</v>
       </c>
       <c r="B50" t="n">
-        <v>58057</v>
+        <v>58136</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5592,37 +5564,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Frängvallen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469482</v>
+        <v>469463</v>
       </c>
       <c r="R50" t="n">
-        <v>6859388</v>
+        <v>6859422</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5651,7 +5627,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5661,7 +5637,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5676,22 +5657,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132038592</v>
+        <v>135254338</v>
       </c>
       <c r="B51" t="n">
-        <v>58079</v>
+        <v>58136</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5699,37 +5680,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469603</v>
+        <v>469453</v>
       </c>
       <c r="R51" t="n">
-        <v>6859383</v>
+        <v>6859464</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5753,22 +5743,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5783,60 +5763,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134675963</v>
+        <v>129633772</v>
       </c>
       <c r="B52" t="n">
-        <v>108205</v>
+        <v>58057</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220083</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Frängvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469655</v>
+        <v>469482</v>
       </c>
       <c r="R52" t="n">
-        <v>6859352</v>
+        <v>6859388</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5860,12 +5840,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5880,69 +5870,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134678455</v>
+        <v>132038592</v>
       </c>
       <c r="B53" t="n">
-        <v>99099</v>
+        <v>58079</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220093</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>469482</v>
+        <v>469603</v>
       </c>
       <c r="R53" t="n">
-        <v>6859439</v>
+        <v>6859383</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5966,12 +5947,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5986,22 +5977,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134675994</v>
+        <v>134675963</v>
       </c>
       <c r="B54" t="n">
-        <v>108274</v>
+        <v>108205</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6009,21 +6000,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6095,10 +6086,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134675983</v>
+        <v>134678455</v>
       </c>
       <c r="B55" t="n">
-        <v>110150</v>
+        <v>99099</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6106,37 +6097,46 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220294</v>
+        <v>220093</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469655</v>
+        <v>469482</v>
       </c>
       <c r="R55" t="n">
-        <v>6859352</v>
+        <v>6859439</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6180,71 +6180,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129602811</v>
+        <v>135464559</v>
       </c>
       <c r="B56" t="n">
-        <v>99118</v>
+        <v>99099</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>469660</v>
+        <v>469523</v>
       </c>
       <c r="R56" t="n">
-        <v>6859439</v>
+        <v>6859380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6271,22 +6257,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6301,57 +6277,66 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129648410</v>
+        <v>135464843</v>
       </c>
       <c r="B57" t="n">
-        <v>99118</v>
+        <v>99099</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>469726</v>
+        <v>469530</v>
       </c>
       <c r="R57" t="n">
-        <v>6859290</v>
+        <v>6859327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6378,12 +6363,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6398,60 +6383,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132038598</v>
+        <v>135464914</v>
       </c>
       <c r="B58" t="n">
-        <v>99195</v>
+        <v>99099</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469533</v>
+        <v>469524</v>
       </c>
       <c r="R58" t="n">
-        <v>6859346</v>
+        <v>6859337</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6475,22 +6469,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6505,60 +6489,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132038599</v>
+        <v>134675994</v>
       </c>
       <c r="B59" t="n">
-        <v>99195</v>
+        <v>108274</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>469528</v>
+        <v>469655</v>
       </c>
       <c r="R59" t="n">
-        <v>6859347</v>
+        <v>6859352</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6582,22 +6566,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6612,60 +6586,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132038600</v>
+        <v>134675983</v>
       </c>
       <c r="B60" t="n">
-        <v>99195</v>
+        <v>110150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469464</v>
+        <v>469655</v>
       </c>
       <c r="R60" t="n">
-        <v>6859415</v>
+        <v>6859352</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6689,22 +6663,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6719,22 +6683,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132038601</v>
+        <v>129602811</v>
       </c>
       <c r="B61" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6759,20 +6723,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469448</v>
+        <v>469660</v>
       </c>
       <c r="R61" t="n">
-        <v>6859488</v>
+        <v>6859439</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6801,7 +6779,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6811,7 +6789,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6838,10 +6816,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132038608</v>
+        <v>129648410</v>
       </c>
       <c r="B62" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6869,17 +6847,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Frägnvallen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469511</v>
+        <v>469726</v>
       </c>
       <c r="R62" t="n">
-        <v>6859411</v>
+        <v>6859290</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6906,19 +6884,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6933,19 +6901,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132038609</v>
+        <v>132038598</v>
       </c>
       <c r="B63" t="n">
         <v>99195</v>
@@ -6980,10 +6948,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469467</v>
+        <v>469533</v>
       </c>
       <c r="R63" t="n">
-        <v>6859441</v>
+        <v>6859346</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7015,7 +6983,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7025,7 +6993,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7052,7 +7020,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134674521</v>
+        <v>132038599</v>
       </c>
       <c r="B64" t="n">
         <v>99195</v>
@@ -7083,17 +7051,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469509</v>
+        <v>469528</v>
       </c>
       <c r="R64" t="n">
-        <v>6859411</v>
+        <v>6859347</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7117,12 +7085,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7137,19 +7115,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134917738</v>
+        <v>132038600</v>
       </c>
       <c r="B65" t="n">
         <v>99195</v>
@@ -7177,29 +7155,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469433</v>
+        <v>469464</v>
       </c>
       <c r="R65" t="n">
-        <v>6859503</v>
+        <v>6859415</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7223,12 +7192,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7243,60 +7222,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134675822</v>
+        <v>132038601</v>
       </c>
       <c r="B66" t="n">
-        <v>109924</v>
+        <v>99195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221184</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469649</v>
+        <v>469448</v>
       </c>
       <c r="R66" t="n">
-        <v>6859353</v>
+        <v>6859488</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7320,12 +7299,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7340,56 +7329,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129648001</v>
+        <v>132038608</v>
       </c>
       <c r="B67" t="n">
-        <v>97977</v>
+        <v>99195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Frägnvallen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469753</v>
+        <v>469511</v>
       </c>
       <c r="R67" t="n">
-        <v>6859437</v>
+        <v>6859411</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7416,78 +7409,87 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134674574</v>
+        <v>132038609</v>
       </c>
       <c r="B68" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469517</v>
+        <v>469467</v>
       </c>
       <c r="R68" t="n">
-        <v>6859380</v>
+        <v>6859441</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7511,12 +7513,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7531,44 +7543,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134674601</v>
+        <v>134674521</v>
       </c>
       <c r="B69" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7578,13 +7590,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>469529</v>
+        <v>469509</v>
       </c>
       <c r="R69" t="n">
-        <v>6859380</v>
+        <v>6859411</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7640,48 +7652,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134675109</v>
+        <v>134917738</v>
       </c>
       <c r="B70" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>469556</v>
+        <v>469433</v>
       </c>
       <c r="R70" t="n">
-        <v>6859367</v>
+        <v>6859503</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7705,12 +7726,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7737,48 +7758,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134675710</v>
+        <v>135464370</v>
       </c>
       <c r="B71" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469628</v>
+        <v>469441</v>
       </c>
       <c r="R71" t="n">
-        <v>6859357</v>
+        <v>6859505</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7802,12 +7823,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7822,60 +7843,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134675713</v>
+        <v>135464406</v>
       </c>
       <c r="B72" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469623</v>
+        <v>469438</v>
       </c>
       <c r="R72" t="n">
-        <v>6859347</v>
+        <v>6859495</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7899,12 +7920,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7931,32 +7952,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134675870</v>
+        <v>135464455</v>
       </c>
       <c r="B73" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7966,10 +7987,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469615</v>
+        <v>469493</v>
       </c>
       <c r="R73" t="n">
-        <v>6859312</v>
+        <v>6859424</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7996,12 +8017,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8028,32 +8049,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134676123</v>
+        <v>135464484</v>
       </c>
       <c r="B74" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8063,13 +8084,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469670</v>
+        <v>469492</v>
       </c>
       <c r="R74" t="n">
-        <v>6859325</v>
+        <v>6859409</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8093,12 +8114,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8113,60 +8134,69 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134918089</v>
+        <v>135464501</v>
       </c>
       <c r="B75" t="n">
-        <v>79963</v>
+        <v>99195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469469</v>
+        <v>469495</v>
       </c>
       <c r="R75" t="n">
-        <v>6859389</v>
+        <v>6859403</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8190,12 +8220,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8210,15 +8240,2848 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135464522</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>469487</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6859380</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135464534</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>469518</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6859381</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135464582</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>469505</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6859375</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135464597</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>469526</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6859371</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135464616</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>469498</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6859362</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135464763</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>469560</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6859301</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135464867</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>469525</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6859330</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135464894</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>469523</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6859339</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135464922</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>469531</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6859335</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135464966</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>469549</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6859405</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>10 blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135465048</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>469545</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6859417</v>
+      </c>
+      <c r="S86" t="n">
+        <v>20</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135465147</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>469489</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6859408</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>134675822</v>
+      </c>
+      <c r="B88" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>469649</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6859353</v>
+      </c>
+      <c r="S88" t="n">
+        <v>20</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135464933</v>
+      </c>
+      <c r="B89" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>469531</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6859335</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129648001</v>
+      </c>
+      <c r="B90" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Frägnvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>469753</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6859437</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>134674574</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>469517</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6859380</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>134674601</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>469529</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6859380</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>134675109</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>469556</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6859367</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>134675710</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>469628</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6859357</v>
+      </c>
+      <c r="S94" t="n">
+        <v>20</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>134675713</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>469623</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6859347</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>134675870</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>469615</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6859312</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>134676123</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>469670</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6859325</v>
+      </c>
+      <c r="S97" t="n">
+        <v>20</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>135464505</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>469497</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6859405</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>135464575</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>469525</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6859377</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>135464639</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>469567</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6859371</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>135464683</v>
+      </c>
+      <c r="B101" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>469616</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6859340</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>135465123</v>
+      </c>
+      <c r="B102" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Lill-Frägnet, Lill-Frägnet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>469489</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6859408</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>134918089</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>469469</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6859389</v>
+      </c>
+      <c r="S103" t="n">
+        <v>15</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY103"/>
+  <dimension ref="A1:AZ103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129602546</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129602294</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038585</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038586</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675398</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134918036</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135465062</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038582</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129576469</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129577131</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1911,6 +1971,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129577275</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129577297</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,6 +2175,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129577349</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129577427</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2299,6 +2379,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129577487</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633776</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2513,6 +2603,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633777</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633778</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2727,6 +2827,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633779</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2824,6 +2929,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648005</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2921,6 +3031,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648006</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648007</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3115,6 +3235,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648008</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3212,6 +3337,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648009</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3309,6 +3439,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648010</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3406,6 +3541,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648011</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3503,6 +3643,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648012</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3600,6 +3745,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648015</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3697,6 +3847,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648413</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3795,6 +3950,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129657344</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3893,6 +4053,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129657346</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3991,6 +4156,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129657347</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4104,6 +4274,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038618</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4217,6 +4392,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038622</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4324,6 +4504,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038631</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4421,6 +4606,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675467</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4518,6 +4708,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134676077</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4625,6 +4820,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633773</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4732,6 +4932,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038593</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4839,6 +5044,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038590</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4946,6 +5156,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038591</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5043,6 +5258,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134918047</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5140,6 +5360,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135465024</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5251,6 +5476,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254319</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5348,6 +5578,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129647998</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5453,6 +5688,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648407</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5550,6 +5790,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129657334</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5666,6 +5911,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038583</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5772,6 +6022,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254338</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5879,6 +6134,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633772</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5986,6 +6246,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038592</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6083,6 +6348,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675963</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6189,6 +6459,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134678455</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6286,6 +6561,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464559</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6392,6 +6672,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464843</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6498,6 +6783,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464914</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6595,6 +6885,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675994</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6692,6 +6987,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675983</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6813,6 +7113,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129602811</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6910,6 +7215,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648410</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7017,6 +7327,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038598</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7124,6 +7439,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038599</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7231,6 +7551,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038600</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7338,6 +7663,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038601</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7445,6 +7775,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038608</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7552,6 +7887,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038609</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7649,6 +7989,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134674521</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7755,6 +8100,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134917738</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7852,6 +8202,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464370</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7949,6 +8304,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464406</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8046,6 +8406,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464455</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8143,6 +8508,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464484</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8249,6 +8619,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464501</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8360,6 +8735,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464522</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8457,6 +8837,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464534</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8568,6 +8953,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464582</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8665,6 +9055,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464597</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8776,6 +9171,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464616</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8882,6 +9282,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464763</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8979,6 +9384,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464867</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9076,6 +9486,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464894</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9182,6 +9597,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464922</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9298,6 +9718,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464966</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9409,6 +9834,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135465048</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9515,6 +9945,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135465147</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9612,6 +10047,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675822</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9709,6 +10149,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464933</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9803,6 +10248,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129648001</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9900,6 +10350,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134674574</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9997,6 +10452,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134674601</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10094,6 +10554,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675109</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10191,6 +10656,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675710</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10288,6 +10758,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675713</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10385,6 +10860,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675870</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10482,6 +10962,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134676123</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10588,6 +11073,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464505</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10694,6 +11184,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464575</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10791,6 +11286,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464639</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10888,6 +11388,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135464683</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10985,6 +11490,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135465123</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11082,8 +11592,117 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134918089</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -1355,7 +1355,7 @@
         <v>134918036</v>
       </c>
       <c r="B8" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135465062</v>
       </c>
       <c r="B9" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>134918047</v>
       </c>
       <c r="B44" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>135465024</v>
       </c>
       <c r="B45" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>135254319</v>
       </c>
       <c r="B46" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>135254338</v>
       </c>
       <c r="B51" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>135464559</v>
       </c>
       <c r="B56" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>135464843</v>
       </c>
       <c r="B57" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>135464914</v>
       </c>
       <c r="B58" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>134917738</v>
       </c>
       <c r="B70" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>135464370</v>
       </c>
       <c r="B71" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>135464406</v>
       </c>
       <c r="B72" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>135464455</v>
       </c>
       <c r="B73" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>135464484</v>
       </c>
       <c r="B74" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>135464501</v>
       </c>
       <c r="B75" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>135464522</v>
       </c>
       <c r="B76" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135464534</v>
       </c>
       <c r="B77" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>135464582</v>
       </c>
       <c r="B78" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>135464597</v>
       </c>
       <c r="B79" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>135464616</v>
       </c>
       <c r="B80" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>135464763</v>
       </c>
       <c r="B81" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>135464867</v>
       </c>
       <c r="B82" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>135464894</v>
       </c>
       <c r="B83" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>135464922</v>
       </c>
       <c r="B84" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>135464966</v>
       </c>
       <c r="B85" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>135465048</v>
       </c>
       <c r="B86" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>135465147</v>
       </c>
       <c r="B87" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>135464933</v>
       </c>
       <c r="B89" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>135464505</v>
       </c>
       <c r="B98" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>135464575</v>
       </c>
       <c r="B99" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>135464639</v>
       </c>
       <c r="B100" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>135464683</v>
       </c>
       <c r="B101" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>135465123</v>
       </c>
       <c r="B102" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>134918089</v>
       </c>
       <c r="B103" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -1125,7 +1125,7 @@
         <v>135697992</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>135697325</v>
       </c>
       <c r="B66" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>135698799</v>
       </c>
       <c r="B67" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>135698249</v>
       </c>
       <c r="B68" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>135464559</v>
       </c>
       <c r="B71" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>135464843</v>
       </c>
       <c r="B72" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>135464914</v>
       </c>
       <c r="B73" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135697058</v>
       </c>
       <c r="B74" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>135464370</v>
       </c>
       <c r="B87" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>135464406</v>
       </c>
       <c r="B88" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>135464455</v>
       </c>
       <c r="B89" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>135464484</v>
       </c>
       <c r="B90" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>135464501</v>
       </c>
       <c r="B91" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>135464522</v>
       </c>
       <c r="B92" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>135464534</v>
       </c>
       <c r="B93" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>135464582</v>
       </c>
       <c r="B94" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>135464597</v>
       </c>
       <c r="B95" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>135464616</v>
       </c>
       <c r="B96" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>135464763</v>
       </c>
       <c r="B97" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>135464867</v>
       </c>
       <c r="B98" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>135464894</v>
       </c>
       <c r="B99" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>135464922</v>
       </c>
       <c r="B100" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>135464966</v>
       </c>
       <c r="B101" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>135465048</v>
       </c>
       <c r="B102" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>135465147</v>
       </c>
       <c r="B103" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>135697087</v>
       </c>
       <c r="B104" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135697139</v>
       </c>
       <c r="B105" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135697159</v>
       </c>
       <c r="B106" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>135697224</v>
       </c>
       <c r="B107" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>135697274</v>
       </c>
       <c r="B108" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>135697323</v>
       </c>
       <c r="B109" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>135697396</v>
       </c>
       <c r="B110" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>135697562</v>
       </c>
       <c r="B111" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>135697735</v>
       </c>
       <c r="B112" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135697833</v>
       </c>
       <c r="B113" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>135698043</v>
       </c>
       <c r="B114" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135698107</v>
       </c>
       <c r="B115" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>135698144</v>
       </c>
       <c r="B116" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>135698169</v>
       </c>
       <c r="B117" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>135698172</v>
       </c>
       <c r="B118" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>135698502</v>
       </c>
       <c r="B119" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>135698519</v>
       </c>
       <c r="B120" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>135698525</v>
       </c>
       <c r="B121" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>135698542</v>
       </c>
       <c r="B122" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>135698558</v>
       </c>
       <c r="B123" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>135698592</v>
       </c>
       <c r="B124" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>135698758</v>
       </c>
       <c r="B125" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>135699137</v>
       </c>
       <c r="B126" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>135699138</v>
       </c>
       <c r="B127" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>135699206</v>
       </c>
       <c r="B128" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>135464933</v>
       </c>
       <c r="B130" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>135699042</v>
       </c>
       <c r="B131" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>135464505</v>
       </c>
       <c r="B140" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135464575</v>
       </c>
       <c r="B141" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>135464639</v>
       </c>
       <c r="B142" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>135464683</v>
       </c>
       <c r="B143" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>135465123</v>
       </c>
       <c r="B144" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>135697293</v>
       </c>
       <c r="B145" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>135699146</v>
       </c>
       <c r="B146" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135697969</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135697992</v>
       </c>
       <c r="B6" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135465062</v>
       </c>
       <c r="B11" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>135697189</v>
       </c>
       <c r="B12" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>135697575</v>
       </c>
       <c r="B13" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>135697169</v>
       </c>
       <c r="B44" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>135698120</v>
       </c>
       <c r="B45" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>135698564</v>
       </c>
       <c r="B46" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>135699239</v>
       </c>
       <c r="B47" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>135465024</v>
       </c>
       <c r="B53" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135697181</v>
       </c>
       <c r="B54" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>135697299</v>
       </c>
       <c r="B55" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>135697666</v>
       </c>
       <c r="B56" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>135699113</v>
       </c>
       <c r="B63" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>135697325</v>
       </c>
       <c r="B66" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>135698799</v>
       </c>
       <c r="B67" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>135698249</v>
       </c>
       <c r="B68" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>135464559</v>
       </c>
       <c r="B71" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>135464843</v>
       </c>
       <c r="B72" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>135464914</v>
       </c>
       <c r="B73" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135697058</v>
       </c>
       <c r="B74" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>135464370</v>
       </c>
       <c r="B87" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>135464406</v>
       </c>
       <c r="B88" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>135464455</v>
       </c>
       <c r="B89" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>135464484</v>
       </c>
       <c r="B90" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>135464501</v>
       </c>
       <c r="B91" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>135464522</v>
       </c>
       <c r="B92" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>135464534</v>
       </c>
       <c r="B93" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>135464582</v>
       </c>
       <c r="B94" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>135464597</v>
       </c>
       <c r="B95" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>135464616</v>
       </c>
       <c r="B96" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>135464763</v>
       </c>
       <c r="B97" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>135464867</v>
       </c>
       <c r="B98" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>135464894</v>
       </c>
       <c r="B99" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>135464922</v>
       </c>
       <c r="B100" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>135464966</v>
       </c>
       <c r="B101" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>135465048</v>
       </c>
       <c r="B102" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>135465147</v>
       </c>
       <c r="B103" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>135697087</v>
       </c>
       <c r="B104" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135697139</v>
       </c>
       <c r="B105" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135697159</v>
       </c>
       <c r="B106" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>135697224</v>
       </c>
       <c r="B107" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>135697274</v>
       </c>
       <c r="B108" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>135697323</v>
       </c>
       <c r="B109" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>135697396</v>
       </c>
       <c r="B110" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>135697562</v>
       </c>
       <c r="B111" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>135697735</v>
       </c>
       <c r="B112" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135697833</v>
       </c>
       <c r="B113" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>135698043</v>
       </c>
       <c r="B114" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135698107</v>
       </c>
       <c r="B115" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>135698144</v>
       </c>
       <c r="B116" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>135698169</v>
       </c>
       <c r="B117" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>135698172</v>
       </c>
       <c r="B118" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>135698502</v>
       </c>
       <c r="B119" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>135698519</v>
       </c>
       <c r="B120" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>135698525</v>
       </c>
       <c r="B121" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>135698542</v>
       </c>
       <c r="B122" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>135698558</v>
       </c>
       <c r="B123" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>135698592</v>
       </c>
       <c r="B124" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>135698758</v>
       </c>
       <c r="B125" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>135699137</v>
       </c>
       <c r="B126" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>135699138</v>
       </c>
       <c r="B127" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>135699206</v>
       </c>
       <c r="B128" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>135464933</v>
       </c>
       <c r="B130" t="n">
-        <v>110014</v>
+        <v>110037</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>135699042</v>
       </c>
       <c r="B131" t="n">
-        <v>110014</v>
+        <v>110037</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>135464505</v>
       </c>
       <c r="B140" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135464575</v>
       </c>
       <c r="B141" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>135464639</v>
       </c>
       <c r="B142" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>135464683</v>
       </c>
       <c r="B143" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>135465123</v>
       </c>
       <c r="B144" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>135697293</v>
       </c>
       <c r="B145" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>135699146</v>
       </c>
       <c r="B146" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135697969</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135697992</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>135697189</v>
       </c>
       <c r="B12" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>135697575</v>
       </c>
       <c r="B13" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>135697169</v>
       </c>
       <c r="B44" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>135698120</v>
       </c>
       <c r="B45" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>135698564</v>
       </c>
       <c r="B46" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>135699239</v>
       </c>
       <c r="B47" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135697181</v>
       </c>
       <c r="B54" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>135697299</v>
       </c>
       <c r="B55" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>135697666</v>
       </c>
       <c r="B56" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>135697325</v>
       </c>
       <c r="B66" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>135698799</v>
       </c>
       <c r="B67" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>135698249</v>
       </c>
       <c r="B68" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135697058</v>
       </c>
       <c r="B74" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>135697087</v>
       </c>
       <c r="B104" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135697139</v>
       </c>
       <c r="B105" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135697159</v>
       </c>
       <c r="B106" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>135697224</v>
       </c>
       <c r="B107" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>135697274</v>
       </c>
       <c r="B108" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>135697323</v>
       </c>
       <c r="B109" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>135697396</v>
       </c>
       <c r="B110" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>135697562</v>
       </c>
       <c r="B111" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>135697735</v>
       </c>
       <c r="B112" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135697833</v>
       </c>
       <c r="B113" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>135698043</v>
       </c>
       <c r="B114" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135698107</v>
       </c>
       <c r="B115" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>135698144</v>
       </c>
       <c r="B116" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>135698169</v>
       </c>
       <c r="B117" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>135698172</v>
       </c>
       <c r="B118" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>135698502</v>
       </c>
       <c r="B119" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>135698519</v>
       </c>
       <c r="B120" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>135698525</v>
       </c>
       <c r="B121" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>135698542</v>
       </c>
       <c r="B122" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>135698558</v>
       </c>
       <c r="B123" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>135698592</v>
       </c>
       <c r="B124" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>135698758</v>
       </c>
       <c r="B125" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>135699137</v>
       </c>
       <c r="B126" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>135699138</v>
       </c>
       <c r="B127" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>135699206</v>
       </c>
       <c r="B128" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>135699042</v>
       </c>
       <c r="B131" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>135697293</v>
       </c>
       <c r="B145" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>135699146</v>
       </c>
       <c r="B146" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -1125,7 +1125,7 @@
         <v>135697992</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>135697325</v>
       </c>
       <c r="B66" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>135698799</v>
       </c>
       <c r="B67" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>135698249</v>
       </c>
       <c r="B68" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135697058</v>
       </c>
       <c r="B74" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>135697087</v>
       </c>
       <c r="B104" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135697139</v>
       </c>
       <c r="B105" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135697159</v>
       </c>
       <c r="B106" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>135697224</v>
       </c>
       <c r="B107" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>135697274</v>
       </c>
       <c r="B108" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>135697323</v>
       </c>
       <c r="B109" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>135697396</v>
       </c>
       <c r="B110" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>135697562</v>
       </c>
       <c r="B111" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>135697735</v>
       </c>
       <c r="B112" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135697833</v>
       </c>
       <c r="B113" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>135698043</v>
       </c>
       <c r="B114" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135698107</v>
       </c>
       <c r="B115" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>135698144</v>
       </c>
       <c r="B116" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>135698169</v>
       </c>
       <c r="B117" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>135698172</v>
       </c>
       <c r="B118" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>135698502</v>
       </c>
       <c r="B119" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>135698519</v>
       </c>
       <c r="B120" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>135698525</v>
       </c>
       <c r="B121" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>135698542</v>
       </c>
       <c r="B122" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>135698558</v>
       </c>
       <c r="B123" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>135698592</v>
       </c>
       <c r="B124" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>135698758</v>
       </c>
       <c r="B125" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>135699137</v>
       </c>
       <c r="B126" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>135699138</v>
       </c>
       <c r="B127" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>135699206</v>
       </c>
       <c r="B128" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>135699042</v>
       </c>
       <c r="B131" t="n">
-        <v>110039</v>
+        <v>110040</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>135697293</v>
       </c>
       <c r="B145" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>135699146</v>
       </c>
       <c r="B146" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135697969</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135697992</v>
       </c>
       <c r="B6" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>135697189</v>
       </c>
       <c r="B12" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>135697575</v>
       </c>
       <c r="B13" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>135697169</v>
       </c>
       <c r="B44" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>135698120</v>
       </c>
       <c r="B45" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>135698564</v>
       </c>
       <c r="B46" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>135699239</v>
       </c>
       <c r="B47" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135697181</v>
       </c>
       <c r="B54" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>135697299</v>
       </c>
       <c r="B55" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>135697666</v>
       </c>
       <c r="B56" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>135699113</v>
       </c>
       <c r="B63" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>135697325</v>
       </c>
       <c r="B66" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>135698799</v>
       </c>
       <c r="B67" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>135698249</v>
       </c>
       <c r="B68" t="n">
-        <v>99330</v>
+        <v>99331</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135697058</v>
       </c>
       <c r="B74" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>135697087</v>
       </c>
       <c r="B104" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135697139</v>
       </c>
       <c r="B105" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135697159</v>
       </c>
       <c r="B106" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>135697224</v>
       </c>
       <c r="B107" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>135697274</v>
       </c>
       <c r="B108" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>135697323</v>
       </c>
       <c r="B109" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>135697396</v>
       </c>
       <c r="B110" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>135697562</v>
       </c>
       <c r="B111" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>135697735</v>
       </c>
       <c r="B112" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135697833</v>
       </c>
       <c r="B113" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>135698043</v>
       </c>
       <c r="B114" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135698107</v>
       </c>
       <c r="B115" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>135698144</v>
       </c>
       <c r="B116" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>135698169</v>
       </c>
       <c r="B117" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>135698172</v>
       </c>
       <c r="B118" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>135698502</v>
       </c>
       <c r="B119" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>135698519</v>
       </c>
       <c r="B120" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>135698525</v>
       </c>
       <c r="B121" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>135698542</v>
       </c>
       <c r="B122" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>135698558</v>
       </c>
       <c r="B123" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>135698592</v>
       </c>
       <c r="B124" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>135698758</v>
       </c>
       <c r="B125" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>135699137</v>
       </c>
       <c r="B126" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>135699138</v>
       </c>
       <c r="B127" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>135699206</v>
       </c>
       <c r="B128" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>135699042</v>
       </c>
       <c r="B131" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>135697293</v>
       </c>
       <c r="B145" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>135699146</v>
       </c>
       <c r="B146" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135697969</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135697992</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>135697189</v>
       </c>
       <c r="B12" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>135697575</v>
       </c>
       <c r="B13" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>135697169</v>
       </c>
       <c r="B44" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>135698120</v>
       </c>
       <c r="B45" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>135698564</v>
       </c>
       <c r="B46" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>135699239</v>
       </c>
       <c r="B47" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135697181</v>
       </c>
       <c r="B54" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>135697299</v>
       </c>
       <c r="B55" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>135697666</v>
       </c>
       <c r="B56" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>135699113</v>
       </c>
       <c r="B63" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>135697325</v>
       </c>
       <c r="B66" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>135698799</v>
       </c>
       <c r="B67" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>135698249</v>
       </c>
       <c r="B68" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135697058</v>
       </c>
       <c r="B74" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>135697087</v>
       </c>
       <c r="B104" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135697139</v>
       </c>
       <c r="B105" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135697159</v>
       </c>
       <c r="B106" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>135697224</v>
       </c>
       <c r="B107" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>135697274</v>
       </c>
       <c r="B108" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>135697323</v>
       </c>
       <c r="B109" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>135697396</v>
       </c>
       <c r="B110" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>135697562</v>
       </c>
       <c r="B111" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>135697735</v>
       </c>
       <c r="B112" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135697833</v>
       </c>
       <c r="B113" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>135698043</v>
       </c>
       <c r="B114" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135698107</v>
       </c>
       <c r="B115" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>135698144</v>
       </c>
       <c r="B116" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>135698169</v>
       </c>
       <c r="B117" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>135698172</v>
       </c>
       <c r="B118" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>135698502</v>
       </c>
       <c r="B119" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>135698519</v>
       </c>
       <c r="B120" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>135698525</v>
       </c>
       <c r="B121" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>135698542</v>
       </c>
       <c r="B122" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>135698558</v>
       </c>
       <c r="B123" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>135698592</v>
       </c>
       <c r="B124" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>135698758</v>
       </c>
       <c r="B125" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>135699137</v>
       </c>
       <c r="B126" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>135699138</v>
       </c>
       <c r="B127" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>135699206</v>
       </c>
       <c r="B128" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>135699042</v>
       </c>
       <c r="B131" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>135697293</v>
       </c>
       <c r="B145" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>135699146</v>
       </c>
       <c r="B146" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 28384-2026 artfynd.xlsx
+++ b/artfynd/A 28384-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135697969</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135697992</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>135697189</v>
       </c>
       <c r="B12" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>135697575</v>
       </c>
       <c r="B13" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>135697169</v>
       </c>
       <c r="B44" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>135698120</v>
       </c>
       <c r="B45" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>135698564</v>
       </c>
       <c r="B46" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>135699239</v>
       </c>
       <c r="B47" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135697181</v>
       </c>
       <c r="B54" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>135697299</v>
       </c>
       <c r="B55" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>135697666</v>
       </c>
       <c r="B56" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>135699113</v>
       </c>
       <c r="B63" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>135697325</v>
       </c>
       <c r="B66" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>135698799</v>
       </c>
       <c r="B67" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>135698249</v>
       </c>
       <c r="B68" t="n">
-        <v>99337</v>
+        <v>99338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135697058</v>
       </c>
       <c r="B74" t="n">
-        <v>99206</v>
+        <v>99207</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>135697087</v>
       </c>
       <c r="B104" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135697139</v>
       </c>
       <c r="B105" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135697159</v>
       </c>
       <c r="B106" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>135697224</v>
       </c>
       <c r="B107" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>135697274</v>
       </c>
       <c r="B108" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>135697323</v>
       </c>
       <c r="B109" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>135697396</v>
       </c>
       <c r="B110" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>135697562</v>
       </c>
       <c r="B111" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>135697735</v>
       </c>
       <c r="B112" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135697833</v>
       </c>
       <c r="B113" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>135698043</v>
       </c>
       <c r="B114" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135698107</v>
       </c>
       <c r="B115" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>135698144</v>
       </c>
       <c r="B116" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>135698169</v>
       </c>
       <c r="B117" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>135698172</v>
       </c>
       <c r="B118" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>135698502</v>
       </c>
       <c r="B119" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>135698519</v>
       </c>
       <c r="B120" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>135698525</v>
       </c>
       <c r="B121" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>135698542</v>
       </c>
       <c r="B122" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>135698558</v>
       </c>
       <c r="B123" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>135698592</v>
       </c>
       <c r="B124" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>135698758</v>
       </c>
       <c r="B125" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>135699137</v>
       </c>
       <c r="B126" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>135699138</v>
       </c>
       <c r="B127" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>135699206</v>
       </c>
       <c r="B128" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>135699042</v>
       </c>
       <c r="B131" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>135697293</v>
       </c>
       <c r="B145" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>135699146</v>
       </c>
       <c r="B146" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
